--- a/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/03_WIM3 - Müşteri Koruma, Tier-N ve TSB/EKG-KLT-MTR-03_garanti_sonrasi_pfmea_ve_kontrol_plani_guclendirme_matr.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/06_Garanti Sorunları Yönetimi/03_WIM3 - Müşteri Koruma, Tier-N ve TSB/EKG-KLT-MTR-03_garanti_sonrasi_pfmea_ve_kontrol_plani_guclendirme_matr.xlsx
@@ -917,7 +917,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-MTR-03&amp;C&amp;"Arial,Regular"&amp;11Garanti Sonrası PFMEA ve Kontrol Planı Güçlendirme Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: Yapay RPN/başarı skorları kaldırıldı; PFMEA/kontrol planı revizyonu ve ölçülmüş etkinlik kaydına dönüştürüldü.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1083,7 +1084,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-KLT-MTR-03&amp;C&amp;"Arial,Regular"&amp;11Garanti Sonrası PFMEA ve Kontrol Planı Güçlendirme Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: Yapay RPN/başarı skorları kaldırıldı; PFMEA/kontrol planı revizyonu ve ölçülmüş etkinlik kaydına dönüştürüldü.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>